--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-care-next-visit.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-care-next-visit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
